--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586153.7805706561</v>
+        <v>586154</v>
       </c>
       <c r="R2" t="n">
-        <v>6878435.453403552</v>
+        <v>6878435</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1990-06-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586153.7805706561</v>
+        <v>586154</v>
       </c>
       <c r="R3" t="n">
-        <v>6878435.453403552</v>
+        <v>6878435</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -875,19 +855,9 @@
           <t>1990-06-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-06-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586153.7805706561</v>
+        <v>586154</v>
       </c>
       <c r="R4" t="n">
-        <v>6878435.453403552</v>
+        <v>6878435</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1001,19 +966,9 @@
           <t>1990-06-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-06-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98613</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>82368161</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>82368176</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>82368174</v>
       </c>
       <c r="B4" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8446-2022 artfynd.xlsx
+++ b/artfynd/A 8446-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82368161</v>
+        <v>82368174</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82368176</v>
+        <v>82368161</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82368174</v>
+        <v>82368176</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,23 +908,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>223597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
